--- a/MySQL_Optimization.xlsx
+++ b/MySQL_Optimization.xlsx
@@ -5,30 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\QuintetCompany\projects\mini_dbms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\QuintetCompany\projects\mini_dbms\mini_dbms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963486E4-9293-4A4B-A435-2A5BC5F04CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351CE5EB-98FE-4522-8B72-FBB091BB65D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Optimization_System" sheetId="38" r:id="rId1"/>
-    <sheet name="Overview" sheetId="1" r:id="rId2"/>
-    <sheet name="SQL_Statements" sheetId="24" r:id="rId3"/>
-    <sheet name="Indexes" sheetId="25" r:id="rId4"/>
-    <sheet name="Database_Structure" sheetId="26" r:id="rId5"/>
-    <sheet name="InnoDB_Tables" sheetId="27" r:id="rId6"/>
-    <sheet name="MyISAM_Tables" sheetId="28" r:id="rId7"/>
-    <sheet name="MEMORY_Tables" sheetId="29" r:id="rId8"/>
-    <sheet name="Query_Execution_Plan" sheetId="30" r:id="rId9"/>
-    <sheet name="Query_Optimizer" sheetId="31" r:id="rId10"/>
-    <sheet name="Buffering_&amp;_Caching" sheetId="32" r:id="rId11"/>
-    <sheet name="Optimizing_Locking" sheetId="33" r:id="rId12"/>
-    <sheet name="Optimizing_MySQL_Server" sheetId="34" r:id="rId13"/>
-    <sheet name="Measuring_Performance" sheetId="35" r:id="rId14"/>
-    <sheet name="Examining_Server_Thread" sheetId="36" r:id="rId15"/>
-    <sheet name="Tracing_Optimizer" sheetId="37" r:id="rId16"/>
+    <sheet name="Color" sheetId="39" r:id="rId1"/>
+    <sheet name="Optimization_System" sheetId="38" r:id="rId2"/>
+    <sheet name="Overview" sheetId="1" r:id="rId3"/>
+    <sheet name="SQL_Statements" sheetId="24" r:id="rId4"/>
+    <sheet name="Indexes" sheetId="25" r:id="rId5"/>
+    <sheet name="Database_Structure" sheetId="26" r:id="rId6"/>
+    <sheet name="InnoDB_Tables" sheetId="27" r:id="rId7"/>
+    <sheet name="MyISAM_Tables" sheetId="28" r:id="rId8"/>
+    <sheet name="MEMORY_Tables" sheetId="29" r:id="rId9"/>
+    <sheet name="Query_Execution_Plan" sheetId="30" r:id="rId10"/>
+    <sheet name="Query_Optimizer" sheetId="31" r:id="rId11"/>
+    <sheet name="Buffering_&amp;_Caching" sheetId="32" r:id="rId12"/>
+    <sheet name="Optimizing_Locking" sheetId="33" r:id="rId13"/>
+    <sheet name="Optimizing_MySQL_Server" sheetId="34" r:id="rId14"/>
+    <sheet name="Measuring_Performance" sheetId="35" r:id="rId15"/>
+    <sheet name="Examining_Server_Thread" sheetId="36" r:id="rId16"/>
+    <sheet name="Tracing_Optimizer" sheetId="37" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="144">
   <si>
     <t>Definition No</t>
   </si>
@@ -1078,62 +1079,93 @@
     <t>3. Optimizing DELETE Statements</t>
   </si>
   <si>
-    <t>NDB Cluster là gì??</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Step 01:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Check is whether you can add an index. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - Set up indexes on columns used in the WHERE clause, to speed up evaluation, filtering, and the final retrieval of results.
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WHERE clause optimization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 
 </t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>To avoid wasted disk space, construct a small set of indexes that speed up many related queries used in your application.</t>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Optimizer-side logic normalization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>early filtering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index eligibility</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sargable = Search ARGument ABLE</t>
     </r>
     <r>
       <rPr>
@@ -1150,67 +1182,97 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Step 02:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Isolate and tune any part of the query, such as a function call, that takes excessive time.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - Depending on how the query is structured, a function could be called once for every row in the result set, or even once for every row in the table, greatly magnifying any inefficiency.
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Một điều kiện WHERE được gọi là sargable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nếu </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MySQL có thể dùng nó</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để thực hiện </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index lookup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index range scan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Step 03:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Minimize the number of full table scans in your queries, particularly for big tables.</t>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quy tắc của Sargable:</t>
     </r>
     <r>
       <rPr>
@@ -1227,11 +1289,787 @@
       <rPr>
         <b/>
         <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column phải đứng một mình:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
         <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>column</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>operator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">constant]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không được:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Column nằm trong function
+ - Column nằm trong biểu thức toán học
+ - Column bị ép kiểu ngầm (implicit cast)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ví dụ:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sargable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WHERE age = 18
+WHERE age &gt; 18
+WHERE age BETWEEN 18 AND 25
+WHERE created_at &gt;= '2025-01-01'
+=&gt; MySQL:
+ - Biết bắt đầu từ đâu
+ - Biết dừng ở đâu trong B-tree index
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Not sargable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WHERE YEAR(created_at) = 2025
+WHERE age + 1 = 18
+WHERE UPPER(name) = 'JOHN'
+WHERE price * 2 &gt; 100
+=&gt; MySQL:
+ - Phải tính toán cho từng row
+ - Không dùng index
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Điều kiện</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">             </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Is Sargable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lý do</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+col = 5                        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                  Direct lookup
+col &gt; 5                        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                  Range scan
+col IN (1,2,3)              </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                  Multiple lookups
+col LIKE 'abc%'           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                   Prefix range
+col LIKE '%abc'           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                   Không có start point
+FUNC(col) = x             </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                  Index không áp dụng
+col + 1 = x                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                  Expression trên col</t>
+    </r>
+  </si>
+  <si>
+    <t>1.1. Sargable conditions là gì?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">MySQL đã tự động tối ưu logic trong WHERE clause trước khi optimizer chọn execution plan.
+The optimizations performed by MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1. Removal of unnecessary parentheses</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  ((a AND b) AND c OR (((a AND b) AND (c AND d))))
+  =&gt; (a AND b AND c) OR (a AND b AND c AND d)
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. Constant folding (Gộp hằng số)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  (a &lt; b AND b = c) AND a = 5
+  =&gt; b &gt; 5 AND b = c AND a = 5
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. Constant condition removal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  (b = 5 AND b = 5) OR (b = 6 AND 5 = 5) OR (b = 7 AND 5 = 6)
+  =&gt; b = 5 OR b = 6
+  During preparation rather than during the optimization phase, simplification of joins
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ý nghĩa của 3 loại optimizations trên:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. Remove parentheses</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+   =&gt; Tối ưu: Logic Boolean 
+   =&gt; Ảnh hưởng: Giảm độ phức tạp biểu thức
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. Constant folding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+   =&gt; Tối ưu: Phép toán với hằng số
+   =&gt; Ảnh hưởng: Giảm phép tính runtime
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. Constant removal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+   =&gt; Tối ưu: Điều kiện luôn đúng/sai
+   =&gt; Ảnh hưởng: Loại bỏ nhánh vô nghĩa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>==&gt; CPU optimization nhẹ, không phải I/O</t>
+    </r>
+  </si>
+  <si>
+    <t>Level 1</t>
+  </si>
+  <si>
+    <t>Level 2</t>
+  </si>
+  <si>
+    <t>Level 3</t>
+  </si>
+  <si>
+    <t>Level 4</t>
+  </si>
+  <si>
+    <t>Level 5</t>
+  </si>
+  <si>
+    <t>Level 6</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 01:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Index
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Có index cho WHERE / JOIN / ORDER BY / GROUP BY chưa?
+ - Ưu tiên Ít index nhưng đúng và dùng lại được nhiều query.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 02:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hàm trong query</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Có function / expression trong SELECT, WHERE, JOIN không?
+ - Nó bị gọi mỗi row hay mỗi table scan?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 03:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Full Table Scan
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Có full table scan không?
+ - Bảng lớn → full scan = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cảnh báo đỏ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Step 04:</t>
     </r>
     <r>
@@ -1243,7 +2081,143 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Keep table statistics up to date by using the ANALYZE TABLE statement periodically</t>
+      <t xml:space="preserve"> Statistics
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Đã chạy ANALYZE TABLE chưa?
+ - Optimizer có stats đúng để chọn plan không?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 05:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Storage Engine–specific
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Query này chạy trên InnoDB / MyISAM?
+ - Có áp dụng đúng tuning + index + config cho engine đó không?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 06:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">InnoDB Read-Only Optimization
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Query chỉ đọc?
+ - Có dùng read-only transaction / consistent read chưa?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 07:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Query Simplicity</t>
     </r>
     <r>
       <rPr>
@@ -1254,73 +2228,445 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
- - The optimizer has the information needed to construct an efficient execution plan.
+ - Query có bị viết quá phức tạp không?
+ - Optimizer does some of the same transformations automatically
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 08:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXPLAIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - If a performance issue is not easily solved by one of the basic guidelines, investigate the internal details of the specific query.
+ - Đã đọc EXPLAIN plan chưa?
+ - Key dùng là gì? rows ước lượng bao nhiêu? extra có gì lạ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 09:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cache / Memory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Buffer pool / key cache / query cache đủ chưa?
+ - Query có được hưởng cache không?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 10:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scalability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Query chạy nhanh nhờ cache → OK
+ - Nhưng có ăn quá nhiều memory không?
+ - Load tăng thì có sập hiệu năng không?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 11:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Locking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Query có bị lock chờ session khác không?
+ - Có tranh chấp đọc/ghi không?
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
         <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Step 05:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tuning techniques, indexing techniques, and configuration parameters</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> that are specific to the storage engine for each table.
+      <t>1.2. Don't try to rewrite your queries to make arithmetic operations faster, while sacrificing readability.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Step 06:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Optimize single-query transactions for InnoDB tables (Read-Only Transactions)
-Step 07: Avoid transforming the query in ways that make it hard to understand, especially if the optimizer does some of the same transformations automatically.</t>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tự tay làm những việc này thay vì optimizer thì không đem lại:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. Không tạo index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. Không giảm full table scan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. Không thay đổi access path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>==&gt; Viết rõ ràng, dễ đọc thường không chậm hơn (Đừng cố viết phức tạp)</t>
+    </r>
+  </si>
+  <si>
+    <t>1.3. Constant expressions used by indexes are evaluated only once.</t>
+  </si>
+  <si>
+    <t>WHERE col &gt; (100 + 20)
+=&gt; (100 + 20) được tính trước khi scan, không phải mỗi row.</t>
+  </si>
+  <si>
+    <t>c TINYINT UNSIGNED   -- range: 0..255
+WHERE c &lt; 256
+Điều kiện luôn đúng, nên optimizer biến thành:
+WHERE 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.4. Constant folding &amp; range check
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Optimizer hiểu kiểu dữ liệu
+ - Nó tự loại bỏ điều kiện vô nghĩa</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> - MyISAM lưu row count table information for MyISAM and MEMORY tables
+ - InnoDB không (do MVCC)</t>
+  </si>
+  <si>
+    <t>1.5. COUNT(*) on a single table without a WHERE nhanh chỉ với MyISAM / MEMORY</t>
+  </si>
+  <si>
+    <t>1.6. Early detection of invalid constant expressions.</t>
+  </si>
+  <si>
+    <t>WHERE a = 1 AND a = 2
+Optimizer phát hiện vô lý → trả về rỗng ngay.
+Không scan, không IO.</t>
+  </si>
+  <si>
+    <t>1.7. HAVING is merged with WHERE if you do not use GROUP BY or aggregate functions (COUNT(), MIN()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT * FROM t HAVING a &gt; 5;
+→ Không GROUP BY → chuyển thành:
+SELECT * FROM t WHERE a &gt; 5;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vì WHERE:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Dùng index được
+ - Filter sớm hơn</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Một table được xem là constant table nếu optimizer CHẮC CHẮN rằng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - Kết quả của table đó là 0 hoặc 1 row, trước khi JOIN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.8. All constant tables are read first before any other tables in the query.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A constant table is any of the following:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - An empty table or a table with one row.
+ - A table that is used with a WHERE clause on 
+   + A PRIMARY KEY or A UNIQUE index
+   + All index parts are compared to constant expressions and are defined as NOT NULL.</t>
     </r>
   </si>
 </sst>
@@ -1328,7 +2674,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1390,8 +2736,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1399,13 +2746,59 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1421,6 +2814,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1526,7 +2961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1573,16 +3008,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1600,37 +3068,58 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1912,6 +3401,1877 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63EBCB4E-F3A1-47DC-8023-F5D3158CADDF}">
+  <dimension ref="B4:C10"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="39"/>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="40"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="52"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="43"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="45"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="47"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="48"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589F1E26-0146-4D4B-9E3E-D18BA9E16206}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC9B955-0E92-4B2A-A450-D6764B0D61B7}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616F7A75-6636-41D0-A5BF-C09A53A4743D}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643B35D6-A09D-4BE6-9CBD-986014316153}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C015D492-E55E-4470-A9AA-71874542BFB2}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B2A83-DAF9-43E9-836F-550864651867}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A906BADD-5292-47B3-B69D-69CFB0A9F400}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9292E335-6000-4F28-8F83-0CE4DA1A5AEB}">
+  <dimension ref="B2:I44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BE99AE-3ECE-44D1-A26E-485A069D1C69}">
   <dimension ref="B1:E44"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -1935,7 +5295,7 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="49" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1943,19 +5303,19 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="16"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="16"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="49" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1963,25 +5323,25 @@
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="16"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="16"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="16"/>
+      <c r="B10" s="49"/>
       <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="49" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1989,13 +5349,13 @@
       </c>
     </row>
     <row r="13" spans="2:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="16"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="49" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -2003,7 +5363,7 @@
       </c>
     </row>
     <row r="16" spans="2:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="16"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
@@ -2047,1596 +5407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC9B955-0E92-4B2A-A450-D6764B0D61B7}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616F7A75-6636-41D0-A5BF-C09A53A4743D}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643B35D6-A09D-4BE6-9CBD-986014316153}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C015D492-E55E-4470-A9AA-71874542BFB2}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B2A83-DAF9-43E9-836F-550864651867}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A906BADD-5292-47B3-B69D-69CFB0A9F400}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9292E335-6000-4F28-8F83-0CE4DA1A5AEB}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:O27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -3663,10 +5434,10 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -3675,13 +5446,13 @@
       <c r="F3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="16"/>
-      <c r="C4" s="27"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="4" t="s">
         <v>28</v>
       </c>
@@ -3691,16 +5462,16 @@
       <c r="F4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="17"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="16"/>
-      <c r="C5" s="28"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="17"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D6" s="13"/>
@@ -3712,7 +5483,7 @@
       </c>
     </row>
     <row r="8" spans="2:15" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="27" t="s">
         <v>36</v>
       </c>
       <c r="I8" s="4" t="s">
@@ -3720,13 +5491,13 @@
       </c>
     </row>
     <row r="9" spans="2:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="H9" s="19"/>
+      <c r="H9" s="29"/>
       <c r="I9" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="27" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="4" t="s">
@@ -3734,7 +5505,7 @@
       </c>
     </row>
     <row r="11" spans="2:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="H11" s="19"/>
+      <c r="H11" s="29"/>
       <c r="I11" s="4" t="s">
         <v>41</v>
       </c>
@@ -3757,37 +5528,37 @@
       </c>
     </row>
     <row r="14" spans="2:15" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="N14" s="23"/>
-      <c r="O14" s="24"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="35"/>
     </row>
     <row r="15" spans="2:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="L15" s="25"/>
-      <c r="M15" s="20" t="s">
+      <c r="L15" s="28"/>
+      <c r="M15" s="31" t="s">
         <v>60</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O15" s="20" t="s">
+      <c r="O15" s="31" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="L16" s="25"/>
-      <c r="M16" s="21"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="32"/>
       <c r="N16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="21"/>
+      <c r="O16" s="32"/>
     </row>
     <row r="17" spans="12:15" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="L17" s="25"/>
+      <c r="L17" s="28"/>
       <c r="M17" s="15" t="s">
         <v>61</v>
       </c>
@@ -3795,7 +5566,7 @@
       <c r="O17" s="15"/>
     </row>
     <row r="18" spans="12:15" ht="78" x14ac:dyDescent="0.3">
-      <c r="L18" s="25"/>
+      <c r="L18" s="28"/>
       <c r="M18" s="15" t="s">
         <v>62</v>
       </c>
@@ -3805,7 +5576,7 @@
       </c>
     </row>
     <row r="19" spans="12:15" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="L19" s="25"/>
+      <c r="L19" s="28"/>
       <c r="M19" s="15" t="s">
         <v>63</v>
       </c>
@@ -3817,7 +5588,7 @@
       </c>
     </row>
     <row r="20" spans="12:15" ht="140.4" x14ac:dyDescent="0.3">
-      <c r="L20" s="25"/>
+      <c r="L20" s="28"/>
       <c r="M20" s="15" t="s">
         <v>64</v>
       </c>
@@ -3829,7 +5600,7 @@
       </c>
     </row>
     <row r="21" spans="12:15" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="L21" s="19"/>
+      <c r="L21" s="29"/>
       <c r="M21" s="15" t="s">
         <v>65</v>
       </c>
@@ -3839,18 +5610,18 @@
       <c r="O21" s="15"/>
     </row>
     <row r="22" spans="12:15" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L22" s="18" t="s">
+      <c r="L22" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="M22" s="30" t="s">
+      <c r="M22" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="N22" s="31"/>
-      <c r="O22" s="32"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="26"/>
     </row>
     <row r="23" spans="12:15" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="L23" s="25"/>
-      <c r="M23" s="33" t="s">
+      <c r="L23" s="28"/>
+      <c r="M23" s="16" t="s">
         <v>69</v>
       </c>
       <c r="N23" s="4" t="s">
@@ -3859,8 +5630,8 @@
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="12:15" ht="124.8" x14ac:dyDescent="0.3">
-      <c r="L24" s="25"/>
-      <c r="M24" s="34" t="s">
+      <c r="L24" s="28"/>
+      <c r="M24" s="17" t="s">
         <v>66</v>
       </c>
       <c r="N24" s="4" t="s">
@@ -3869,8 +5640,8 @@
       <c r="O24" s="4"/>
     </row>
     <row r="25" spans="12:15" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="L25" s="25"/>
-      <c r="M25" s="34" t="s">
+      <c r="L25" s="28"/>
+      <c r="M25" s="17" t="s">
         <v>67</v>
       </c>
       <c r="N25" s="4" t="s">
@@ -3879,8 +5650,8 @@
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="12:15" ht="78" x14ac:dyDescent="0.3">
-      <c r="L26" s="19"/>
-      <c r="M26" s="34" t="s">
+      <c r="L26" s="29"/>
+      <c r="M26" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N26" s="4" t="s">
@@ -3916,452 +5687,590 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE6619B-9EFE-467D-8800-103128E5CAD9}">
-  <dimension ref="B2:F73"/>
+  <dimension ref="B2:H85"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
     <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="40.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="50.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="70.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="60.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="80.77734375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="50.77734375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+    <row r="2" spans="2:8" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="296.39999999999998" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E3" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="50" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="2:8" ht="280.8" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D5" s="28"/>
+      <c r="E5" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="390" x14ac:dyDescent="0.3">
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D6" s="28"/>
+      <c r="E6" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+    </row>
+    <row r="7" spans="2:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D7" s="28"/>
+      <c r="E7" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+    </row>
+    <row r="8" spans="2:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="28"/>
+      <c r="E8" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+    </row>
+    <row r="9" spans="2:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D9" s="28"/>
+      <c r="E9" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+    </row>
+    <row r="10" spans="2:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D10" s="28"/>
+      <c r="E10" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+    </row>
+    <row r="11" spans="2:8" ht="93.6" x14ac:dyDescent="0.3">
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D11" s="28"/>
+      <c r="E11" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+    </row>
+    <row r="12" spans="2:8" ht="300" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="28"/>
+      <c r="E12" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="28"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D14" s="28"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D15" s="28"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D16" s="28"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
-      <c r="D17" s="25"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
-      <c r="D18" s="25"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
-      <c r="D19" s="25"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
-      <c r="D20" s="25"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
-      <c r="D21" s="25"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="25"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="25"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="25"/>
+      <c r="D24" s="28"/>
       <c r="E24" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="25"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="19"/>
+      <c r="D26" s="28"/>
       <c r="E26" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="78" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D27" s="28"/>
+      <c r="E27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="26"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="46.8" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
-      <c r="D33" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D33" s="28"/>
+      <c r="E33" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D34" s="28"/>
+      <c r="E34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="4"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="26"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="4" t="s">
-        <v>113</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="F36" s="4"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="4" t="s">
-        <v>114</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="28"/>
+      <c r="D38" s="29"/>
       <c r="E38" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="2:6" ht="78" x14ac:dyDescent="0.3">
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="34" t="s">
-        <v>82</v>
+      <c r="D39" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="4"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="4"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="4"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-    </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-    </row>
-    <row r="53" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-    </row>
-    <row r="59" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-    </row>
-    <row r="60" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-    </row>
-    <row r="62" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-    </row>
-    <row r="63" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-    </row>
-    <row r="64" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
     </row>
     <row r="65" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
     </row>
     <row r="66" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
     </row>
     <row r="67" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
     </row>
     <row r="68" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
     </row>
     <row r="69" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E69" s="9"/>
@@ -4383,17 +6292,65 @@
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
     </row>
+    <row r="74" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+    </row>
+    <row r="76" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+    </row>
+    <row r="78" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+    </row>
+    <row r="80" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+    </row>
+    <row r="81" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+    </row>
+    <row r="82" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+    </row>
+    <row r="83" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+    </row>
+    <row r="84" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+    </row>
+    <row r="85" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="D4:D26"/>
-    <mergeCell ref="D28:D32"/>
-    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D4:D38"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="D48:D50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4DAB14-8BEB-49D0-A974-E459552043C0}">
   <dimension ref="B2:I44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4477,8 +6434,8 @@
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H12" s="8"/>
@@ -4620,7 +6577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E758AC8F-CE92-4A74-B11F-18F83FF0DFB6}">
   <dimension ref="B2:I44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4704,8 +6661,8 @@
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H12" s="8"/>
@@ -4847,7 +6804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F3656E-0437-4FA9-9B39-E8B47F67A6B9}">
   <dimension ref="B2:I44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4931,8 +6888,8 @@
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H12" s="8"/>
@@ -5074,7 +7031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27C2A0C-FCD6-4AA8-A154-7209C0870F44}">
   <dimension ref="B2:I44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5158,8 +7115,8 @@
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H12" s="8"/>
@@ -5301,7 +7258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF5DA6E-5872-4AD9-A457-973E001C42B4}">
   <dimension ref="B2:I44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5385,235 +7342,8 @@
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589F1E26-0146-4D4B-9E3E-D18BA9E16206}">
-  <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="70.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="50.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H12" s="8"/>
